--- a/data/trans_dic/IP16A10-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A10-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  medicamentos para la diarrea</t>
+          <t>Menores que consumiero  medicamentos para la diarrea (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,86; 25,12</t>
+          <t>2,95; 24,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,14</t>
+          <t>0,0; 10,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,57</t>
+          <t>0,0; 16,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 14,69</t>
+          <t>1,42; 13,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,22</t>
+          <t>0,0; 6,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,19</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,58</t>
+          <t>0,0; 19,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 4,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,57</t>
+          <t>0,0; 15,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,94</t>
+          <t>0,0; 18,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,35</t>
+          <t>0,0; 11,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 3,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 12,73</t>
+          <t>1,46; 13,67</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,62; 38,2</t>
+          <t>4,75; 39,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,33</t>
+          <t>0,0; 16,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,01</t>
+          <t>0,0; 13,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 18,28</t>
+          <t>2,03; 17,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,84</t>
+          <t>0,0; 7,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,43</t>
+          <t>0,0; 10,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 9,68</t>
+          <t>0,83; 9,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,25</t>
+          <t>0,0; 7,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,55</t>
+          <t>0,0; 9,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,69</t>
+          <t>0,0; 4,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,96</t>
+          <t>0,0; 6,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 7,3</t>
+          <t>0,79; 6,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,11</t>
+          <t>0,7; 5,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,85</t>
+          <t>0,57; 5,28</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,42</t>
+          <t>0,0; 20,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,67</t>
+          <t>0,0; 15,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,68</t>
+          <t>0,0; 8,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,81</t>
+          <t>0,0; 7,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,0</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,24</t>
+          <t>0,0; 23,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,87</t>
+          <t>0,0; 26,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,88</t>
+          <t>0,0; 20,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,03</t>
+          <t>0,0; 15,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,44; 10,51</t>
+          <t>3,32; 10,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 4,27</t>
+          <t>0,68; 4,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,4</t>
+          <t>0,35; 3,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,57</t>
+          <t>0,5; 4,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 4,24</t>
+          <t>0,7; 4,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,61</t>
+          <t>0,47; 4,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,24; 5,97</t>
+          <t>2,38; 6,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,24</t>
+          <t>0,95; 3,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,71</t>
+          <t>0,43; 2,82</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero  medicamentos para la diarrea (tasa de respuesta: 99,57%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1488</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2174</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>447; 3684</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3440</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>520; 5083</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3304</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1976</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3788</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3188</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4082</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4318</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>619; 5795</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1765</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2432</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>527; 4394</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2619</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3012</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>671; 5745</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2555</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1266</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1149</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2676</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1848</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3875</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>504; 5794</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4066</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3630</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3326</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2867</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>607; 5239</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>932; 6947</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>564; 5259</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1044</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1044</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3891</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5262</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3729</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5308</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1252</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1252</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2655</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3902</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3899</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4177</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>6797</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>3296</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1762</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>3445</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>9516</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>6741</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>3824</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>3639; 11202</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1209; 7191</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>554; 4764</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>671; 6739</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1248; 7358</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>662; 6211</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>5843; 14742</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>3391; 12701</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1289; 8370</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A10-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A10-Clase-trans_dic.xlsx
@@ -678,12 +678,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 24,29</t>
+          <t>2,83; 24,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,19</t>
+          <t>0,0; 11,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,03</t>
+          <t>0,0; 14,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 13,88</t>
+          <t>1,43; 15,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,38</t>
+          <t>0,0; 8,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,49</t>
+          <t>0,0; 19,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,84</t>
+          <t>0,0; 15,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,34</t>
+          <t>0,0; 18,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,58</t>
+          <t>0,0; 11,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 13,67</t>
+          <t>1,43; 12,94</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,75; 39,55</t>
+          <t>4,56; 38,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,41</t>
+          <t>0,0; 18,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,72</t>
+          <t>0,0; 15,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 17,38</t>
+          <t>1,94; 15,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,47</t>
+          <t>0,0; 9,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,28</t>
+          <t>0,0; 11,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 9,58</t>
+          <t>0,84; 9,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,19</t>
+          <t>0,0; 7,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,36</t>
+          <t>0,0; 10,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,61</t>
+          <t>0,0; 3,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,67</t>
+          <t>0,0; 8,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 6,85</t>
+          <t>0,8; 7,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 5,24</t>
+          <t>0,69; 5,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,28</t>
+          <t>0,55; 4,59</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,64</t>
+          <t>0,0; 17,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,65</t>
+          <t>0,0; 15,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,72</t>
+          <t>0,0; 8,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,45</t>
+          <t>0,0; 7,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,95</t>
+          <t>0,0; 26,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,72</t>
+          <t>0,0; 14,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,9</t>
+          <t>0,0; 16,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,32; 10,21</t>
+          <t>3,51; 10,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,03</t>
+          <t>0,64; 4,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,05</t>
+          <t>0,0; 2,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,98</t>
+          <t>0,51; 5,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,13</t>
+          <t>0,7; 4,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,42</t>
+          <t>0,46; 4,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,38; 6,02</t>
+          <t>2,22; 5,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,56</t>
+          <t>0,93; 3,26</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,82</t>
+          <t>0,47; 2,81</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>447; 3684</t>
+          <t>430; 3732</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2732</t>
+          <t>0; 3085</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3440</t>
+          <t>0; 3124</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>520; 5083</t>
+          <t>525; 5517</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3304</t>
+          <t>0; 4312</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3788</t>
+          <t>0; 3814</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3188</t>
+          <t>0; 3157</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4082</t>
+          <t>0; 4168</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4318</t>
+          <t>0; 4333</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>619; 5795</t>
+          <t>605; 5484</t>
         </is>
       </c>
     </row>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>527; 4394</t>
+          <t>506; 4315</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2619</t>
+          <t>0; 3004</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3012</t>
+          <t>0; 3366</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>671; 5745</t>
+          <t>640; 5249</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2555</t>
+          <t>0; 3203</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3875</t>
+          <t>0; 4445</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>504; 5794</t>
+          <t>509; 5944</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4066</t>
+          <t>0; 4341</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3630</t>
+          <t>0; 4136</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3326</t>
+          <t>0; 2725</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2867</t>
+          <t>0; 3552</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>607; 5239</t>
+          <t>612; 5395</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>932; 6947</t>
+          <t>912; 7291</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>564; 5259</t>
+          <t>550; 4568</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3891</t>
+          <t>0; 3260</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5262</t>
+          <t>0; 5307</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3729</t>
+          <t>0; 3742</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 5308</t>
+          <t>0; 5444</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2655</t>
+          <t>0; 2656</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3902</t>
+          <t>0; 3833</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3899</t>
+          <t>0; 2634</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4177</t>
+          <t>0; 4232</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3639; 11202</t>
+          <t>3853; 11462</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1209; 7191</t>
+          <t>1140; 7337</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>554; 4764</t>
+          <t>0; 4665</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>671; 6739</t>
+          <t>686; 6870</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1248; 7358</t>
+          <t>1254; 7788</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>662; 6211</t>
+          <t>652; 6080</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5843; 14742</t>
+          <t>5434; 14637</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3391; 12701</t>
+          <t>3315; 11618</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1289; 8370</t>
+          <t>1395; 8336</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A10-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A10-Clase-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  medicamentos para la diarrea (tasa de respuesta: 99,57%)</t>
+          <t>Menores que consumieron  medicamentos para la diarrea (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,27 +625,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>9,81%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2,41%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 24,6</t>
+          <t>0,0; 14,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,56</t>
+          <t>2,86; 25,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 12,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 15,06</t>
+          <t>1,44; 14,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,33</t>
+          <t>0,0; 6,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6,12%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>6,35%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>3,05%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,68</t>
+          <t>0,0; 17,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 19,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,72</t>
+          <t>0,0; 16,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,62</t>
+          <t>0,0; 10,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 12,94</t>
+          <t>1,42; 12,73</t>
         </is>
       </c>
     </row>
@@ -845,27 +845,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>15,89%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>3,93%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,04%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,56; 38,84</t>
+          <t>0,0; 14,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,33</t>
+          <t>4,62; 38,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 17,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,94; 15,88</t>
+          <t>1,99; 18,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,37</t>
+          <t>0,0; 9,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>3,36%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>3,35%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,03%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,8</t>
+          <t>0,0; 10,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 9,83</t>
+          <t>0,0; 4,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,67</t>
+          <t>0,0; 7,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,66</t>
+          <t>0,0; 10,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,78</t>
+          <t>0,84; 9,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,26</t>
+          <t>0,0; 7,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,05</t>
+          <t>0,81; 7,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 5,5</t>
+          <t>0,49; 5,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,59</t>
+          <t>0,55; 4,85</t>
         </is>
       </c>
     </row>
@@ -1065,27 +1065,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>5,54%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,58%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 14,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1133,12 +1133,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 19,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,75</t>
+          <t>0,0; 7,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,64</t>
+          <t>0,0; 7,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1175,27 +1175,27 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5,66%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8,65%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5,66%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>8,65%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 28,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 26,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,0</t>
+          <t>0,0; 14,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,11</t>
+          <t>0,0; 15,03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>6,19%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1,85%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1,13%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,51; 10,45</t>
+          <t>0,49; 4,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 4,12</t>
+          <t>0,71; 4,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,98</t>
+          <t>0,47; 3,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,08</t>
+          <t>3,44; 10,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,37</t>
+          <t>0,64; 4,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,33</t>
+          <t>0,36; 3,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,22; 5,97</t>
+          <t>2,24; 5,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,26</t>
+          <t>0,92; 3,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,81</t>
+          <t>0,45; 2,71</t>
         </is>
       </c>
     </row>
@@ -1432,20 +1432,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  medicamentos para la diarrea (tasa de respuesta: 99,57%)</t>
+          <t>Menores que consumieron  medicamentos para la diarrea (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1533,27 +1533,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1586,27 +1586,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>1488</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>645</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>430; 3732</t>
+          <t>0; 3128</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3085</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3124</t>
+          <t>435; 3810</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3254</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>525; 5517</t>
+          <t>529; 5383</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4312</t>
+          <t>0; 3218</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1696,32 +1696,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1749,32 +1749,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1233</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>613</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1363</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3814</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3157</t>
+          <t>0; 3993</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3805</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4168</t>
+          <t>0; 3335</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4333</t>
+          <t>0; 3861</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>605; 5484</t>
+          <t>604; 5397</t>
         </is>
       </c>
     </row>
@@ -1859,27 +1859,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1912,27 +1912,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>1765</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>627</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>506; 4315</t>
+          <t>0; 3076</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3004</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3366</t>
+          <t>513; 4244</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2766</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>640; 5249</t>
+          <t>658; 6044</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3203</t>
+          <t>0; 3365</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2022,32 +2022,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>1266</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1149</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4445</t>
+          <t>0; 4092</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>509; 5944</t>
+          <t>0; 3379</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4341</t>
+          <t>0; 3425</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4136</t>
+          <t>0; 3931</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 2725</t>
+          <t>506; 5853</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3552</t>
+          <t>0; 4103</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>612; 5395</t>
+          <t>623; 5585</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>912; 7291</t>
+          <t>654; 6776</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>550; 4568</t>
+          <t>549; 4830</t>
         </is>
       </c>
     </row>
@@ -2185,14 +2185,14 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2200,12 +2200,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2238,27 +2238,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>1044</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3260</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4932</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3661</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5307</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3742</t>
+          <t>0; 3284</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 5444</t>
+          <t>0; 5566</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2348,12 +2348,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2363,12 +2363,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>642</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2416,12 +2416,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3201</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3889</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2656</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3833</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 2634</t>
+          <t>0; 2801</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4232</t>
+          <t>0; 3949</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2511,22 +2511,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>3445</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>6797</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>3296</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>1762</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2719</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>3445</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>2062</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3853; 11462</t>
+          <t>663; 6185</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1140; 7337</t>
+          <t>1269; 7555</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4665</t>
+          <t>655; 5063</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>686; 6870</t>
+          <t>3779; 11532</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1254; 7788</t>
+          <t>1135; 7610</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>652; 6080</t>
+          <t>564; 5323</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5434; 14637</t>
+          <t>5485; 14619</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3315; 11618</t>
+          <t>3296; 11552</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1395; 8336</t>
+          <t>1326; 8046</t>
         </is>
       </c>
     </row>
